--- a/venv/foody/output/thống kê import.xlsx
+++ b/venv/foody/output/thống kê import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\Code_python\venv\foody\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F0D588-BA7E-46A2-87A1-57072965CED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5D72F1-0534-4417-A3BE-FD114608FE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tháng 3" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>tỉnh</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>chưa</t>
-  </si>
-  <si>
-    <t>done</t>
   </si>
 </sst>
 </file>
@@ -407,7 +404,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -415,7 +412,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">

--- a/venv/foody/output/thống kê import.xlsx
+++ b/venv/foody/output/thống kê import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\Code_python\venv\foody\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5D72F1-0534-4417-A3BE-FD114608FE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B472E25-A4B4-4013-BD33-C2E9D6408A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tháng 3" sheetId="1" r:id="rId1"/>
@@ -374,6 +374,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -420,7 +424,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
